--- a/Apparel.xlsx
+++ b/Apparel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Boutiqaat\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A471540-57EA-4B1D-B37E-68E62AEFFFBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37828589-A78C-4D2B-AC43-6E11E69B4E38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Weightage" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">data!$B$1:$L$101</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">data!$A$1:$L$102</definedName>
   </definedNames>
   <calcPr calcId="0"/>
   <extLst>
@@ -1205,7 +1205,7 @@
   <dimension ref="A1:L101"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="40" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
     <col min="4" max="4" width="10.85546875" customWidth="1"/>
@@ -1259,16 +1259,16 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>92</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>91</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E2" t="s">
         <v>14</v>
@@ -1277,13 +1277,13 @@
         <v>16</v>
       </c>
       <c r="G2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I2" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="J2" t="s">
         <v>15</v>
@@ -1292,36 +1292,36 @@
         <v>20</v>
       </c>
       <c r="L2" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>94</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>93</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F3" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="G3" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="H3" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="I3" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="J3" t="s">
         <v>15</v>
@@ -1330,33 +1330,33 @@
         <v>20</v>
       </c>
       <c r="L3" t="s">
-        <v>21</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>29</v>
+        <v>97</v>
       </c>
       <c r="B4" t="s">
-        <v>28</v>
+        <v>96</v>
       </c>
       <c r="C4" t="s">
         <v>13</v>
       </c>
       <c r="D4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E4" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="F4" t="s">
         <v>31</v>
       </c>
       <c r="G4" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="H4" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="I4" t="s">
         <v>19</v>
@@ -1368,106 +1368,106 @@
         <v>20</v>
       </c>
       <c r="L4" t="s">
-        <v>21</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>33</v>
+        <v>104</v>
       </c>
       <c r="B5" t="s">
-        <v>32</v>
+        <v>103</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E5" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="F5" t="s">
         <v>31</v>
       </c>
       <c r="G5" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="H5" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="I5" t="s">
         <v>19</v>
       </c>
       <c r="J5" t="s">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="K5" t="s">
         <v>20</v>
       </c>
       <c r="L5" t="s">
-        <v>21</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>36</v>
+        <v>115</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>114</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E6" t="s">
         <v>38</v>
       </c>
       <c r="F6" t="s">
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="G6" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="H6" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I6" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J6" t="s">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="K6" t="s">
         <v>20</v>
       </c>
       <c r="L6" t="s">
-        <v>21</v>
+        <v>116</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>41</v>
+        <v>118</v>
       </c>
       <c r="B7" t="s">
-        <v>40</v>
+        <v>117</v>
       </c>
       <c r="C7" t="s">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="D7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E7" t="s">
         <v>30</v>
       </c>
       <c r="F7" t="s">
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="G7" t="s">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="H7" t="s">
         <v>15</v>
@@ -1476,7 +1476,7 @@
         <v>19</v>
       </c>
       <c r="J7" t="s">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="K7" t="s">
         <v>20</v>
@@ -1487,69 +1487,69 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>45</v>
+        <v>120</v>
       </c>
       <c r="B8" t="s">
-        <v>44</v>
+        <v>119</v>
       </c>
       <c r="C8" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
       <c r="D8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E8" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="F8" t="s">
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="G8" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="H8" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I8" t="s">
         <v>19</v>
       </c>
       <c r="J8" t="s">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="K8" t="s">
         <v>20</v>
       </c>
       <c r="L8" t="s">
-        <v>21</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>47</v>
+        <v>122</v>
       </c>
       <c r="B9" t="s">
-        <v>46</v>
+        <v>121</v>
       </c>
       <c r="C9" t="s">
-        <v>13</v>
+        <v>123</v>
       </c>
       <c r="D9">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E9" t="s">
         <v>34</v>
       </c>
       <c r="F9" t="s">
-        <v>16</v>
+        <v>124</v>
       </c>
       <c r="G9" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="H9" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I9" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J9" t="s">
         <v>15</v>
@@ -1563,31 +1563,31 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>49</v>
+        <v>126</v>
       </c>
       <c r="B10" t="s">
-        <v>48</v>
+        <v>125</v>
       </c>
       <c r="C10" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="D10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E10" t="s">
-        <v>14</v>
+        <v>53</v>
       </c>
       <c r="F10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G10" t="s">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="H10" t="s">
         <v>15</v>
       </c>
       <c r="I10" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J10" t="s">
         <v>15</v>
@@ -1596,21 +1596,21 @@
         <v>20</v>
       </c>
       <c r="L10" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>50</v>
+        <v>128</v>
       </c>
       <c r="B11" t="s">
-        <v>46</v>
+        <v>127</v>
       </c>
       <c r="C11" t="s">
         <v>13</v>
       </c>
       <c r="D11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E11" t="s">
         <v>34</v>
@@ -1619,7 +1619,7 @@
         <v>16</v>
       </c>
       <c r="G11" t="s">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="H11" t="s">
         <v>15</v>
@@ -1639,25 +1639,25 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>52</v>
+        <v>130</v>
       </c>
       <c r="B12" t="s">
-        <v>51</v>
+        <v>129</v>
       </c>
       <c r="C12" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
       <c r="D12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E12" t="s">
-        <v>53</v>
+        <v>14</v>
       </c>
       <c r="F12" t="s">
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="G12" t="s">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="H12" t="s">
         <v>15</v>
@@ -1666,7 +1666,7 @@
         <v>19</v>
       </c>
       <c r="J12" t="s">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="K12" t="s">
         <v>20</v>
@@ -1677,34 +1677,34 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>55</v>
+        <v>145</v>
       </c>
       <c r="B13" t="s">
-        <v>54</v>
+        <v>144</v>
       </c>
       <c r="C13" t="s">
-        <v>56</v>
+        <v>138</v>
       </c>
       <c r="D13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E13" t="s">
-        <v>30</v>
+        <v>143</v>
       </c>
       <c r="F13" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="G13" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="H13" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="I13" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J13" t="s">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="K13" t="s">
         <v>20</v>
@@ -1715,28 +1715,28 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>58</v>
+        <v>147</v>
       </c>
       <c r="B14" t="s">
-        <v>57</v>
+        <v>146</v>
       </c>
       <c r="C14" t="s">
-        <v>59</v>
+        <v>138</v>
       </c>
       <c r="D14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E14" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="F14" t="s">
         <v>31</v>
       </c>
       <c r="G14" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="H14" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="I14" t="s">
         <v>19</v>
@@ -1753,25 +1753,25 @@
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>62</v>
+        <v>149</v>
       </c>
       <c r="B15" t="s">
-        <v>61</v>
+        <v>148</v>
       </c>
       <c r="C15" t="s">
-        <v>59</v>
+        <v>138</v>
       </c>
       <c r="D15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E15" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="F15" t="s">
         <v>31</v>
       </c>
       <c r="G15" t="s">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="H15" t="s">
         <v>15</v>
@@ -1791,34 +1791,34 @@
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>64</v>
+        <v>150</v>
       </c>
       <c r="B16" t="s">
-        <v>63</v>
+        <v>144</v>
       </c>
       <c r="C16" t="s">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="D16">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E16" t="s">
-        <v>30</v>
+        <v>143</v>
       </c>
       <c r="F16" t="s">
         <v>31</v>
       </c>
       <c r="G16" t="s">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="H16" t="s">
         <v>15</v>
       </c>
       <c r="I16" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J16" t="s">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="K16" t="s">
         <v>20</v>
@@ -1829,34 +1829,34 @@
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>67</v>
+        <v>152</v>
       </c>
       <c r="B17" t="s">
-        <v>66</v>
+        <v>151</v>
       </c>
       <c r="C17" t="s">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="D17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E17" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="F17" t="s">
         <v>31</v>
       </c>
       <c r="G17" t="s">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="H17" t="s">
         <v>15</v>
       </c>
       <c r="I17" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J17" t="s">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="K17" t="s">
         <v>20</v>
@@ -1867,22 +1867,25 @@
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>69</v>
+        <v>154</v>
       </c>
       <c r="B18" t="s">
-        <v>68</v>
+        <v>153</v>
       </c>
       <c r="C18" t="s">
-        <v>13</v>
+        <v>138</v>
+      </c>
+      <c r="D18">
+        <v>4</v>
       </c>
       <c r="E18" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="F18" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="G18" t="s">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="H18" t="s">
         <v>15</v>
@@ -1891,7 +1894,7 @@
         <v>19</v>
       </c>
       <c r="J18" t="s">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="K18" t="s">
         <v>20</v>
@@ -1902,34 +1905,34 @@
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>71</v>
+        <v>156</v>
       </c>
       <c r="B19" t="s">
-        <v>70</v>
+        <v>155</v>
       </c>
       <c r="C19" t="s">
-        <v>72</v>
+        <v>138</v>
       </c>
       <c r="D19">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E19" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="F19" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="G19" t="s">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="H19" t="s">
         <v>15</v>
       </c>
       <c r="I19" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J19" t="s">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="K19" t="s">
         <v>20</v>
@@ -1940,31 +1943,34 @@
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>74</v>
+        <v>158</v>
       </c>
       <c r="B20" t="s">
-        <v>73</v>
+        <v>157</v>
       </c>
       <c r="C20" t="s">
-        <v>72</v>
+        <v>138</v>
+      </c>
+      <c r="D20">
+        <v>4</v>
       </c>
       <c r="E20" t="s">
-        <v>14</v>
+        <v>143</v>
       </c>
       <c r="F20" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="G20" t="s">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="H20" t="s">
         <v>15</v>
       </c>
       <c r="I20" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J20" t="s">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="K20" t="s">
         <v>20</v>
@@ -1975,60 +1981,63 @@
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>76</v>
+        <v>175</v>
       </c>
       <c r="B21" t="s">
-        <v>75</v>
+        <v>174</v>
       </c>
       <c r="C21" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="D21">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E21" t="s">
-        <v>77</v>
+        <v>30</v>
       </c>
       <c r="F21" t="s">
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="G21" t="s">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="H21" t="s">
         <v>15</v>
       </c>
       <c r="I21" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J21" t="s">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="K21" t="s">
         <v>20</v>
       </c>
       <c r="L21" t="s">
-        <v>21</v>
+        <v>116</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>79</v>
+        <v>177</v>
       </c>
       <c r="B22" t="s">
-        <v>78</v>
+        <v>176</v>
       </c>
       <c r="C22" t="s">
-        <v>72</v>
+        <v>65</v>
+      </c>
+      <c r="D22">
+        <v>4</v>
       </c>
       <c r="E22" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F22" t="s">
         <v>16</v>
       </c>
       <c r="G22" t="s">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="H22" t="s">
         <v>15</v>
@@ -2048,34 +2057,34 @@
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>81</v>
+        <v>179</v>
       </c>
       <c r="B23" t="s">
-        <v>80</v>
+        <v>178</v>
       </c>
       <c r="C23" t="s">
-        <v>72</v>
+        <v>13</v>
       </c>
       <c r="D23">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E23" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="F23" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G23" t="s">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="H23" t="s">
         <v>15</v>
       </c>
       <c r="I23" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J23" t="s">
-        <v>15</v>
+        <v>135</v>
       </c>
       <c r="K23" t="s">
         <v>20</v>
@@ -2086,34 +2095,34 @@
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>82</v>
+        <v>181</v>
       </c>
       <c r="B24" t="s">
-        <v>70</v>
+        <v>180</v>
       </c>
       <c r="C24" t="s">
-        <v>72</v>
+        <v>13</v>
       </c>
       <c r="D24">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E24" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="F24" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="G24" t="s">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="H24" t="s">
         <v>15</v>
       </c>
       <c r="I24" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J24" t="s">
-        <v>15</v>
+        <v>135</v>
       </c>
       <c r="K24" t="s">
         <v>20</v>
@@ -2124,34 +2133,34 @@
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>84</v>
+        <v>183</v>
       </c>
       <c r="B25" t="s">
-        <v>83</v>
+        <v>182</v>
       </c>
       <c r="C25" t="s">
-        <v>72</v>
+        <v>184</v>
       </c>
       <c r="D25">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E25" t="s">
-        <v>85</v>
+        <v>30</v>
       </c>
       <c r="F25" t="s">
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="G25" t="s">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="H25" t="s">
         <v>15</v>
       </c>
       <c r="I25" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J25" t="s">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="K25" t="s">
         <v>20</v>
@@ -2162,92 +2171,92 @@
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>86</v>
+        <v>199</v>
       </c>
       <c r="B26" t="s">
-        <v>40</v>
+        <v>198</v>
       </c>
       <c r="C26" t="s">
-        <v>42</v>
+        <v>195</v>
       </c>
       <c r="D26">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E26" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="F26" t="s">
-        <v>15</v>
+        <v>200</v>
       </c>
       <c r="G26" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="H26" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="I26" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J26" t="s">
-        <v>15</v>
+        <v>135</v>
       </c>
       <c r="K26" t="s">
         <v>20</v>
       </c>
       <c r="L26" t="s">
-        <v>21</v>
+        <v>95</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>88</v>
+        <v>206</v>
       </c>
       <c r="B27" t="s">
-        <v>87</v>
+        <v>205</v>
       </c>
       <c r="C27" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="D27">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E27" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F27" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="G27" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H27" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="I27" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J27" t="s">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="K27" t="s">
         <v>20</v>
       </c>
       <c r="L27" t="s">
-        <v>90</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>92</v>
+        <v>208</v>
       </c>
       <c r="B28" t="s">
-        <v>91</v>
+        <v>207</v>
       </c>
       <c r="C28" t="s">
-        <v>42</v>
+        <v>184</v>
       </c>
       <c r="D28">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E28" t="s">
         <v>14</v>
@@ -2262,33 +2271,33 @@
         <v>15</v>
       </c>
       <c r="I28" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J28" t="s">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="K28" t="s">
         <v>20</v>
       </c>
       <c r="L28" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>94</v>
+        <v>216</v>
       </c>
       <c r="B29" t="s">
-        <v>93</v>
+        <v>215</v>
       </c>
       <c r="C29" t="s">
-        <v>59</v>
+        <v>195</v>
       </c>
       <c r="D29">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E29" t="s">
-        <v>30</v>
+        <v>143</v>
       </c>
       <c r="F29" t="s">
         <v>31</v>
@@ -2300,10 +2309,10 @@
         <v>15</v>
       </c>
       <c r="I29" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="J29" t="s">
-        <v>15</v>
+        <v>135</v>
       </c>
       <c r="K29" t="s">
         <v>20</v>
@@ -2314,19 +2323,19 @@
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>97</v>
+        <v>221</v>
       </c>
       <c r="B30" t="s">
-        <v>96</v>
+        <v>220</v>
       </c>
       <c r="C30" t="s">
-        <v>13</v>
+        <v>222</v>
       </c>
       <c r="D30">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E30" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="F30" t="s">
         <v>31</v>
@@ -2347,103 +2356,103 @@
         <v>20</v>
       </c>
       <c r="L30" t="s">
-        <v>95</v>
+        <v>21</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>99</v>
+        <v>226</v>
       </c>
       <c r="B31" t="s">
-        <v>98</v>
+        <v>225</v>
       </c>
       <c r="C31" t="s">
-        <v>59</v>
+        <v>227</v>
       </c>
       <c r="D31">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E31" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F31" t="s">
-        <v>100</v>
+        <v>31</v>
       </c>
       <c r="G31" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="H31" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="I31" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="J31" t="s">
-        <v>15</v>
+        <v>135</v>
       </c>
       <c r="K31" t="s">
         <v>20</v>
       </c>
       <c r="L31" t="s">
-        <v>90</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>102</v>
+        <v>229</v>
       </c>
       <c r="B32" t="s">
-        <v>101</v>
+        <v>228</v>
       </c>
       <c r="C32" t="s">
-        <v>59</v>
+        <v>230</v>
       </c>
       <c r="D32">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E32" t="s">
-        <v>30</v>
+        <v>231</v>
       </c>
       <c r="F32" t="s">
-        <v>100</v>
+        <v>16</v>
       </c>
       <c r="G32" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="H32" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="I32" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="J32" t="s">
-        <v>15</v>
+        <v>135</v>
       </c>
       <c r="K32" t="s">
-        <v>20</v>
+        <v>232</v>
       </c>
       <c r="L32" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>104</v>
+        <v>234</v>
       </c>
       <c r="B33" t="s">
-        <v>103</v>
+        <v>233</v>
       </c>
       <c r="C33" t="s">
-        <v>59</v>
+        <v>230</v>
       </c>
       <c r="D33">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E33" t="s">
-        <v>14</v>
+        <v>235</v>
       </c>
       <c r="F33" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="G33" t="s">
         <v>15</v>
@@ -2452,89 +2461,89 @@
         <v>15</v>
       </c>
       <c r="I33" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J33" t="s">
-        <v>60</v>
+        <v>135</v>
       </c>
       <c r="K33" t="s">
-        <v>20</v>
+        <v>232</v>
       </c>
       <c r="L33" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>106</v>
+        <v>237</v>
       </c>
       <c r="B34" t="s">
-        <v>105</v>
+        <v>236</v>
       </c>
       <c r="C34" t="s">
-        <v>59</v>
+        <v>230</v>
       </c>
       <c r="D34">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E34" t="s">
-        <v>53</v>
+        <v>14</v>
       </c>
       <c r="F34" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="G34" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="H34" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="I34" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J34" t="s">
-        <v>60</v>
+        <v>135</v>
       </c>
       <c r="K34" t="s">
-        <v>20</v>
+        <v>232</v>
       </c>
       <c r="L34" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>108</v>
+        <v>239</v>
       </c>
       <c r="B35" t="s">
-        <v>107</v>
+        <v>238</v>
       </c>
       <c r="C35" t="s">
-        <v>59</v>
+        <v>230</v>
       </c>
       <c r="D35">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E35" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F35" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="G35" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="H35" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="I35" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J35" t="s">
-        <v>60</v>
+        <v>135</v>
       </c>
       <c r="K35" t="s">
-        <v>20</v>
+        <v>232</v>
       </c>
       <c r="L35" t="s">
         <v>95</v>
@@ -2542,124 +2551,124 @@
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>110</v>
+        <v>240</v>
       </c>
       <c r="B36" t="s">
-        <v>109</v>
+        <v>236</v>
       </c>
       <c r="C36" t="s">
-        <v>59</v>
+        <v>230</v>
       </c>
       <c r="D36">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E36" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="F36" t="s">
-        <v>100</v>
+        <v>16</v>
       </c>
       <c r="G36" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="H36" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="I36" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J36" t="s">
-        <v>60</v>
+        <v>135</v>
       </c>
       <c r="K36" t="s">
-        <v>20</v>
+        <v>232</v>
       </c>
       <c r="L36" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>113</v>
+        <v>242</v>
       </c>
       <c r="B37" t="s">
-        <v>112</v>
+        <v>241</v>
       </c>
       <c r="C37" t="s">
-        <v>59</v>
+        <v>230</v>
       </c>
       <c r="D37">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E37" t="s">
-        <v>34</v>
+        <v>212</v>
       </c>
       <c r="F37" t="s">
-        <v>100</v>
+        <v>16</v>
       </c>
       <c r="G37" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="H37" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="I37" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J37" t="s">
-        <v>60</v>
+        <v>135</v>
       </c>
       <c r="K37" t="s">
-        <v>20</v>
+        <v>232</v>
       </c>
       <c r="L37" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>115</v>
+        <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>114</v>
+        <v>35</v>
       </c>
       <c r="C38" t="s">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="D38">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E38" t="s">
         <v>38</v>
       </c>
       <c r="F38" t="s">
-        <v>100</v>
+        <v>16</v>
       </c>
       <c r="G38" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="H38" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I38" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J38" t="s">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="K38" t="s">
         <v>20</v>
       </c>
       <c r="L38" t="s">
-        <v>116</v>
+        <v>21</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="B39" t="s">
-        <v>117</v>
+        <v>98</v>
       </c>
       <c r="C39" t="s">
         <v>59</v>
@@ -2668,36 +2677,36 @@
         <v>5</v>
       </c>
       <c r="E39" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F39" t="s">
         <v>100</v>
       </c>
       <c r="G39" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="H39" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="I39" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="J39" t="s">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="K39" t="s">
         <v>20</v>
       </c>
       <c r="L39" t="s">
-        <v>21</v>
+        <v>90</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="B40" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="C40" t="s">
         <v>59</v>
@@ -2706,54 +2715,54 @@
         <v>5</v>
       </c>
       <c r="E40" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="F40" t="s">
         <v>100</v>
       </c>
       <c r="G40" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="H40" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="I40" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="J40" t="s">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="K40" t="s">
         <v>20</v>
       </c>
       <c r="L40" t="s">
-        <v>111</v>
+        <v>90</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>122</v>
+        <v>23</v>
       </c>
       <c r="B41" t="s">
-        <v>121</v>
+        <v>22</v>
       </c>
       <c r="C41" t="s">
-        <v>123</v>
+        <v>24</v>
       </c>
       <c r="D41">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E41" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="F41" t="s">
-        <v>124</v>
+        <v>15</v>
       </c>
       <c r="G41" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="H41" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="I41" t="s">
         <v>27</v>
@@ -2770,31 +2779,31 @@
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>126</v>
+        <v>29</v>
       </c>
       <c r="B42" t="s">
-        <v>125</v>
+        <v>28</v>
       </c>
       <c r="C42" t="s">
-        <v>65</v>
+        <v>13</v>
       </c>
       <c r="D42">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E42" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="F42" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="G42" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="H42" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="I42" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J42" t="s">
         <v>15</v>
@@ -2803,33 +2812,33 @@
         <v>20</v>
       </c>
       <c r="L42" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>128</v>
+        <v>33</v>
       </c>
       <c r="B43" t="s">
-        <v>127</v>
+        <v>32</v>
       </c>
       <c r="C43" t="s">
         <v>13</v>
       </c>
       <c r="D43">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E43" t="s">
         <v>34</v>
       </c>
       <c r="F43" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="G43" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="H43" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="I43" t="s">
         <v>19</v>
@@ -2846,34 +2855,34 @@
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>130</v>
+        <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>129</v>
+        <v>44</v>
       </c>
       <c r="C44" t="s">
-        <v>59</v>
+        <v>13</v>
       </c>
       <c r="D44">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E44" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="F44" t="s">
-        <v>100</v>
+        <v>16</v>
       </c>
       <c r="G44" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="H44" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I44" t="s">
         <v>19</v>
       </c>
       <c r="J44" t="s">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="K44" t="s">
         <v>20</v>
@@ -2884,34 +2893,34 @@
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>132</v>
+        <v>47</v>
       </c>
       <c r="B45" t="s">
-        <v>131</v>
+        <v>46</v>
       </c>
       <c r="C45" t="s">
-        <v>133</v>
+        <v>13</v>
       </c>
       <c r="D45">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E45" t="s">
         <v>34</v>
       </c>
       <c r="F45" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="G45" t="s">
-        <v>134</v>
+        <v>25</v>
       </c>
       <c r="H45" t="s">
         <v>18</v>
       </c>
       <c r="I45" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J45" t="s">
-        <v>135</v>
+        <v>15</v>
       </c>
       <c r="K45" t="s">
         <v>20</v>
@@ -2922,34 +2931,34 @@
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>137</v>
+        <v>55</v>
       </c>
       <c r="B46" t="s">
-        <v>136</v>
+        <v>54</v>
       </c>
       <c r="C46" t="s">
-        <v>138</v>
+        <v>56</v>
       </c>
       <c r="D46">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E46" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="F46" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="G46" t="s">
         <v>25</v>
       </c>
       <c r="H46" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="I46" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J46" t="s">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="K46" t="s">
         <v>20</v>
@@ -2960,19 +2969,19 @@
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>140</v>
+        <v>58</v>
       </c>
       <c r="B47" t="s">
-        <v>139</v>
+        <v>57</v>
       </c>
       <c r="C47" t="s">
-        <v>138</v>
+        <v>59</v>
       </c>
       <c r="D47">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E47" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="F47" t="s">
         <v>31</v>
@@ -2981,7 +2990,7 @@
         <v>25</v>
       </c>
       <c r="H47" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="I47" t="s">
         <v>19</v>
@@ -2998,34 +3007,34 @@
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>142</v>
+        <v>86</v>
       </c>
       <c r="B48" t="s">
-        <v>141</v>
+        <v>40</v>
       </c>
       <c r="C48" t="s">
-        <v>138</v>
+        <v>42</v>
       </c>
       <c r="D48">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E48" t="s">
-        <v>143</v>
+        <v>30</v>
       </c>
       <c r="F48" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="G48" t="s">
         <v>25</v>
       </c>
       <c r="H48" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="I48" t="s">
         <v>19</v>
       </c>
       <c r="J48" t="s">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="K48" t="s">
         <v>20</v>
@@ -3036,28 +3045,28 @@
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="B49" t="s">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="C49" t="s">
-        <v>138</v>
+        <v>59</v>
       </c>
       <c r="D49">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E49" t="s">
-        <v>143</v>
+        <v>53</v>
       </c>
       <c r="F49" t="s">
         <v>31</v>
       </c>
       <c r="G49" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="H49" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="I49" t="s">
         <v>19</v>
@@ -3069,33 +3078,33 @@
         <v>20</v>
       </c>
       <c r="L49" t="s">
-        <v>21</v>
+        <v>90</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>147</v>
+        <v>108</v>
       </c>
       <c r="B50" t="s">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="C50" t="s">
-        <v>138</v>
+        <v>59</v>
       </c>
       <c r="D50">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E50" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="F50" t="s">
         <v>31</v>
       </c>
       <c r="G50" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="H50" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="I50" t="s">
         <v>19</v>
@@ -3107,33 +3116,33 @@
         <v>20</v>
       </c>
       <c r="L50" t="s">
-        <v>21</v>
+        <v>95</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>149</v>
+        <v>110</v>
       </c>
       <c r="B51" t="s">
-        <v>148</v>
+        <v>109</v>
       </c>
       <c r="C51" t="s">
-        <v>138</v>
+        <v>59</v>
       </c>
       <c r="D51">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E51" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="F51" t="s">
-        <v>31</v>
+        <v>100</v>
       </c>
       <c r="G51" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="H51" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="I51" t="s">
         <v>19</v>
@@ -3145,33 +3154,33 @@
         <v>20</v>
       </c>
       <c r="L51" t="s">
-        <v>21</v>
+        <v>111</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>150</v>
+        <v>113</v>
       </c>
       <c r="B52" t="s">
-        <v>144</v>
+        <v>112</v>
       </c>
       <c r="C52" t="s">
-        <v>138</v>
+        <v>59</v>
       </c>
       <c r="D52">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E52" t="s">
-        <v>143</v>
+        <v>34</v>
       </c>
       <c r="F52" t="s">
-        <v>31</v>
+        <v>100</v>
       </c>
       <c r="G52" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="H52" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="I52" t="s">
         <v>19</v>
@@ -3183,15 +3192,15 @@
         <v>20</v>
       </c>
       <c r="L52" t="s">
-        <v>21</v>
+        <v>111</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>152</v>
+        <v>137</v>
       </c>
       <c r="B53" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="C53" t="s">
         <v>138</v>
@@ -3200,16 +3209,16 @@
         <v>4</v>
       </c>
       <c r="E53" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="F53" t="s">
         <v>31</v>
       </c>
       <c r="G53" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="H53" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I53" t="s">
         <v>19</v>
@@ -3226,10 +3235,10 @@
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>154</v>
+        <v>140</v>
       </c>
       <c r="B54" t="s">
-        <v>153</v>
+        <v>139</v>
       </c>
       <c r="C54" t="s">
         <v>138</v>
@@ -3238,16 +3247,16 @@
         <v>4</v>
       </c>
       <c r="E54" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="F54" t="s">
         <v>31</v>
       </c>
       <c r="G54" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="H54" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I54" t="s">
         <v>19</v>
@@ -3264,10 +3273,10 @@
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="B55" t="s">
-        <v>155</v>
+        <v>141</v>
       </c>
       <c r="C55" t="s">
         <v>138</v>
@@ -3276,16 +3285,16 @@
         <v>4</v>
       </c>
       <c r="E55" t="s">
-        <v>14</v>
+        <v>143</v>
       </c>
       <c r="F55" t="s">
         <v>31</v>
       </c>
       <c r="G55" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="H55" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I55" t="s">
         <v>19</v>
@@ -3302,10 +3311,10 @@
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B56" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C56" t="s">
         <v>138</v>
@@ -3314,16 +3323,16 @@
         <v>4</v>
       </c>
       <c r="E56" t="s">
-        <v>143</v>
+        <v>38</v>
       </c>
       <c r="F56" t="s">
         <v>31</v>
       </c>
       <c r="G56" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="H56" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="I56" t="s">
         <v>19</v>
@@ -3340,10 +3349,10 @@
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B57" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C57" t="s">
         <v>138</v>
@@ -3352,7 +3361,7 @@
         <v>4</v>
       </c>
       <c r="E57" t="s">
-        <v>38</v>
+        <v>143</v>
       </c>
       <c r="F57" t="s">
         <v>31</v>
@@ -3378,10 +3387,10 @@
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B58" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C58" t="s">
         <v>138</v>
@@ -3390,7 +3399,7 @@
         <v>4</v>
       </c>
       <c r="E58" t="s">
-        <v>143</v>
+        <v>38</v>
       </c>
       <c r="F58" t="s">
         <v>31</v>
@@ -3399,7 +3408,7 @@
         <v>25</v>
       </c>
       <c r="H58" t="s">
-        <v>26</v>
+        <v>165</v>
       </c>
       <c r="I58" t="s">
         <v>19</v>
@@ -3416,10 +3425,10 @@
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B59" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C59" t="s">
         <v>138</v>
@@ -3428,7 +3437,7 @@
         <v>4</v>
       </c>
       <c r="E59" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="F59" t="s">
         <v>31</v>
@@ -3454,10 +3463,10 @@
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B60" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C60" t="s">
         <v>138</v>
@@ -3466,7 +3475,7 @@
         <v>4</v>
       </c>
       <c r="E60" t="s">
-        <v>14</v>
+        <v>143</v>
       </c>
       <c r="F60" t="s">
         <v>31</v>
@@ -3492,10 +3501,10 @@
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B61" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C61" t="s">
         <v>138</v>
@@ -3504,7 +3513,7 @@
         <v>4</v>
       </c>
       <c r="E61" t="s">
-        <v>143</v>
+        <v>30</v>
       </c>
       <c r="F61" t="s">
         <v>31</v>
@@ -3513,7 +3522,7 @@
         <v>25</v>
       </c>
       <c r="H61" t="s">
-        <v>165</v>
+        <v>18</v>
       </c>
       <c r="I61" t="s">
         <v>19</v>
@@ -3530,10 +3539,10 @@
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B62" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C62" t="s">
         <v>138</v>
@@ -3542,7 +3551,7 @@
         <v>4</v>
       </c>
       <c r="E62" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="F62" t="s">
         <v>31</v>
@@ -3551,7 +3560,7 @@
         <v>25</v>
       </c>
       <c r="H62" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="I62" t="s">
         <v>19</v>
@@ -3568,22 +3577,22 @@
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="B63" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="C63" t="s">
-        <v>138</v>
+        <v>184</v>
       </c>
       <c r="D63">
         <v>4</v>
       </c>
       <c r="E63" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="F63" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="G63" t="s">
         <v>25</v>
@@ -3606,28 +3615,28 @@
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="B64" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="C64" t="s">
-        <v>59</v>
+        <v>184</v>
       </c>
       <c r="D64">
         <v>4</v>
       </c>
       <c r="E64" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F64" t="s">
-        <v>100</v>
+        <v>16</v>
       </c>
       <c r="G64" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="H64" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="I64" t="s">
         <v>19</v>
@@ -3639,18 +3648,18 @@
         <v>20</v>
       </c>
       <c r="L64" t="s">
-        <v>116</v>
+        <v>21</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="B65" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="C65" t="s">
-        <v>65</v>
+        <v>184</v>
       </c>
       <c r="D65">
         <v>4</v>
@@ -3662,16 +3671,16 @@
         <v>16</v>
       </c>
       <c r="G65" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="H65" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="I65" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J65" t="s">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="K65" t="s">
         <v>20</v>
@@ -3682,34 +3691,34 @@
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="B66" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="C66" t="s">
-        <v>13</v>
+        <v>184</v>
       </c>
       <c r="D66">
         <v>4</v>
       </c>
       <c r="E66" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="F66" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G66" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="H66" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="I66" t="s">
         <v>19</v>
       </c>
       <c r="J66" t="s">
-        <v>135</v>
+        <v>60</v>
       </c>
       <c r="K66" t="s">
         <v>20</v>
@@ -3720,13 +3729,13 @@
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>181</v>
+        <v>202</v>
       </c>
       <c r="B67" t="s">
-        <v>180</v>
+        <v>201</v>
       </c>
       <c r="C67" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
       <c r="D67">
         <v>4</v>
@@ -3735,51 +3744,51 @@
         <v>14</v>
       </c>
       <c r="F67" t="s">
-        <v>31</v>
+        <v>100</v>
       </c>
       <c r="G67" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="H67" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="I67" t="s">
         <v>19</v>
       </c>
       <c r="J67" t="s">
-        <v>135</v>
+        <v>60</v>
       </c>
       <c r="K67" t="s">
         <v>20</v>
       </c>
       <c r="L67" t="s">
-        <v>21</v>
+        <v>90</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>183</v>
+        <v>204</v>
       </c>
       <c r="B68" t="s">
-        <v>182</v>
+        <v>203</v>
       </c>
       <c r="C68" t="s">
-        <v>184</v>
+        <v>59</v>
       </c>
       <c r="D68">
         <v>4</v>
       </c>
       <c r="E68" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="F68" t="s">
         <v>100</v>
       </c>
       <c r="G68" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="H68" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I68" t="s">
         <v>19</v>
@@ -3791,27 +3800,27 @@
         <v>20</v>
       </c>
       <c r="L68" t="s">
-        <v>21</v>
+        <v>111</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>186</v>
+        <v>210</v>
       </c>
       <c r="B69" t="s">
-        <v>185</v>
+        <v>209</v>
       </c>
       <c r="C69" t="s">
-        <v>184</v>
+        <v>211</v>
       </c>
       <c r="D69">
         <v>4</v>
       </c>
       <c r="E69" t="s">
-        <v>30</v>
+        <v>212</v>
       </c>
       <c r="F69" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="G69" t="s">
         <v>25</v>
@@ -3820,36 +3829,36 @@
         <v>26</v>
       </c>
       <c r="I69" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J69" t="s">
-        <v>60</v>
+        <v>135</v>
       </c>
       <c r="K69" t="s">
         <v>20</v>
       </c>
       <c r="L69" t="s">
-        <v>21</v>
+        <v>95</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>188</v>
+        <v>214</v>
       </c>
       <c r="B70" t="s">
-        <v>187</v>
+        <v>213</v>
       </c>
       <c r="C70" t="s">
-        <v>184</v>
+        <v>211</v>
       </c>
       <c r="D70">
         <v>4</v>
       </c>
       <c r="E70" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F70" t="s">
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="G70" t="s">
         <v>25</v>
@@ -3858,10 +3867,10 @@
         <v>26</v>
       </c>
       <c r="I70" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J70" t="s">
-        <v>60</v>
+        <v>135</v>
       </c>
       <c r="K70" t="s">
         <v>20</v>
@@ -3872,13 +3881,13 @@
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>190</v>
+        <v>224</v>
       </c>
       <c r="B71" t="s">
-        <v>189</v>
+        <v>223</v>
       </c>
       <c r="C71" t="s">
-        <v>184</v>
+        <v>59</v>
       </c>
       <c r="D71">
         <v>4</v>
@@ -3887,7 +3896,7 @@
         <v>30</v>
       </c>
       <c r="F71" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="G71" t="s">
         <v>25</v>
@@ -3905,24 +3914,24 @@
         <v>20</v>
       </c>
       <c r="L71" t="s">
-        <v>21</v>
+        <v>90</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>192</v>
+        <v>244</v>
       </c>
       <c r="B72" t="s">
-        <v>191</v>
+        <v>243</v>
       </c>
       <c r="C72" t="s">
-        <v>184</v>
+        <v>230</v>
       </c>
       <c r="D72">
         <v>4</v>
       </c>
       <c r="E72" t="s">
-        <v>34</v>
+        <v>231</v>
       </c>
       <c r="F72" t="s">
         <v>16</v>
@@ -3934,42 +3943,42 @@
         <v>26</v>
       </c>
       <c r="I72" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J72" t="s">
-        <v>60</v>
+        <v>135</v>
       </c>
       <c r="K72" t="s">
-        <v>20</v>
+        <v>232</v>
       </c>
       <c r="L72" t="s">
-        <v>21</v>
+        <v>90</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>194</v>
+        <v>246</v>
       </c>
       <c r="B73" t="s">
-        <v>193</v>
+        <v>245</v>
       </c>
       <c r="C73" t="s">
-        <v>195</v>
+        <v>230</v>
       </c>
       <c r="D73">
         <v>4</v>
       </c>
       <c r="E73" t="s">
-        <v>38</v>
+        <v>231</v>
       </c>
       <c r="F73" t="s">
-        <v>89</v>
+        <v>16</v>
       </c>
       <c r="G73" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="H73" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="I73" t="s">
         <v>27</v>
@@ -3978,36 +3987,36 @@
         <v>135</v>
       </c>
       <c r="K73" t="s">
-        <v>20</v>
+        <v>232</v>
       </c>
       <c r="L73" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>197</v>
+        <v>248</v>
       </c>
       <c r="B74" t="s">
-        <v>196</v>
+        <v>247</v>
       </c>
       <c r="C74" t="s">
-        <v>195</v>
+        <v>230</v>
       </c>
       <c r="D74">
         <v>4</v>
       </c>
       <c r="E74" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="F74" t="s">
-        <v>89</v>
+        <v>16</v>
       </c>
       <c r="G74" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="H74" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="I74" t="s">
         <v>27</v>
@@ -4016,36 +4025,36 @@
         <v>135</v>
       </c>
       <c r="K74" t="s">
-        <v>20</v>
+        <v>232</v>
       </c>
       <c r="L74" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>199</v>
+        <v>250</v>
       </c>
       <c r="B75" t="s">
-        <v>198</v>
+        <v>249</v>
       </c>
       <c r="C75" t="s">
-        <v>195</v>
+        <v>230</v>
       </c>
       <c r="D75">
         <v>4</v>
       </c>
       <c r="E75" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="F75" t="s">
-        <v>200</v>
+        <v>16</v>
       </c>
       <c r="G75" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="H75" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="I75" t="s">
         <v>27</v>
@@ -4054,30 +4063,30 @@
         <v>135</v>
       </c>
       <c r="K75" t="s">
-        <v>20</v>
+        <v>232</v>
       </c>
       <c r="L75" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>202</v>
+        <v>251</v>
       </c>
       <c r="B76" t="s">
-        <v>201</v>
+        <v>247</v>
       </c>
       <c r="C76" t="s">
-        <v>59</v>
+        <v>230</v>
       </c>
       <c r="D76">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E76" t="s">
         <v>14</v>
       </c>
       <c r="F76" t="s">
-        <v>100</v>
+        <v>16</v>
       </c>
       <c r="G76" t="s">
         <v>25</v>
@@ -4086,13 +4095,13 @@
         <v>26</v>
       </c>
       <c r="I76" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J76" t="s">
-        <v>60</v>
+        <v>135</v>
       </c>
       <c r="K76" t="s">
-        <v>20</v>
+        <v>232</v>
       </c>
       <c r="L76" t="s">
         <v>90</v>
@@ -4100,72 +4109,72 @@
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>204</v>
+        <v>253</v>
       </c>
       <c r="B77" t="s">
-        <v>203</v>
+        <v>252</v>
       </c>
       <c r="C77" t="s">
-        <v>59</v>
+        <v>230</v>
       </c>
       <c r="D77">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E77" t="s">
-        <v>14</v>
+        <v>212</v>
       </c>
       <c r="F77" t="s">
-        <v>100</v>
+        <v>16</v>
       </c>
       <c r="G77" t="s">
         <v>25</v>
       </c>
       <c r="H77" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="I77" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J77" t="s">
-        <v>60</v>
+        <v>135</v>
       </c>
       <c r="K77" t="s">
-        <v>20</v>
+        <v>232</v>
       </c>
       <c r="L77" t="s">
-        <v>111</v>
+        <v>90</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>206</v>
+        <v>132</v>
       </c>
       <c r="B78" t="s">
-        <v>205</v>
+        <v>131</v>
       </c>
       <c r="C78" t="s">
-        <v>59</v>
+        <v>133</v>
       </c>
       <c r="D78">
         <v>4</v>
       </c>
       <c r="E78" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F78" t="s">
-        <v>100</v>
+        <v>31</v>
       </c>
       <c r="G78" t="s">
-        <v>15</v>
+        <v>134</v>
       </c>
       <c r="H78" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I78" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J78" t="s">
-        <v>60</v>
+        <v>135</v>
       </c>
       <c r="K78" t="s">
         <v>20</v>
@@ -4176,66 +4185,66 @@
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>208</v>
+        <v>255</v>
       </c>
       <c r="B79" t="s">
-        <v>207</v>
+        <v>254</v>
       </c>
       <c r="C79" t="s">
-        <v>184</v>
+        <v>230</v>
       </c>
       <c r="D79">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E79" t="s">
-        <v>14</v>
+        <v>231</v>
       </c>
       <c r="F79" t="s">
         <v>16</v>
       </c>
       <c r="G79" t="s">
-        <v>15</v>
+        <v>134</v>
       </c>
       <c r="H79" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I79" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J79" t="s">
-        <v>60</v>
+        <v>135</v>
       </c>
       <c r="K79" t="s">
-        <v>20</v>
+        <v>232</v>
       </c>
       <c r="L79" t="s">
-        <v>21</v>
+        <v>95</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>210</v>
+        <v>257</v>
       </c>
       <c r="B80" t="s">
-        <v>209</v>
+        <v>256</v>
       </c>
       <c r="C80" t="s">
-        <v>211</v>
+        <v>230</v>
       </c>
       <c r="D80">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E80" t="s">
-        <v>212</v>
+        <v>235</v>
       </c>
       <c r="F80" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="G80" t="s">
-        <v>25</v>
+        <v>134</v>
       </c>
       <c r="H80" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="I80" t="s">
         <v>27</v>
@@ -4244,7 +4253,7 @@
         <v>135</v>
       </c>
       <c r="K80" t="s">
-        <v>20</v>
+        <v>232</v>
       </c>
       <c r="L80" t="s">
         <v>95</v>
@@ -4252,28 +4261,28 @@
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>214</v>
+        <v>259</v>
       </c>
       <c r="B81" t="s">
-        <v>213</v>
+        <v>258</v>
       </c>
       <c r="C81" t="s">
-        <v>211</v>
+        <v>230</v>
       </c>
       <c r="D81">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E81" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="F81" t="s">
-        <v>100</v>
+        <v>16</v>
       </c>
       <c r="G81" t="s">
-        <v>25</v>
+        <v>134</v>
       </c>
       <c r="H81" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="I81" t="s">
         <v>27</v>
@@ -4282,80 +4291,80 @@
         <v>135</v>
       </c>
       <c r="K81" t="s">
-        <v>20</v>
+        <v>232</v>
       </c>
       <c r="L81" t="s">
-        <v>21</v>
+        <v>95</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>216</v>
+        <v>41</v>
       </c>
       <c r="B82" t="s">
-        <v>215</v>
+        <v>40</v>
       </c>
       <c r="C82" t="s">
-        <v>195</v>
+        <v>42</v>
       </c>
       <c r="D82">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E82" t="s">
-        <v>143</v>
+        <v>30</v>
       </c>
       <c r="F82" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="G82" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="H82" t="s">
         <v>15</v>
       </c>
       <c r="I82" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J82" t="s">
-        <v>135</v>
+        <v>15</v>
       </c>
       <c r="K82" t="s">
         <v>20</v>
       </c>
       <c r="L82" t="s">
-        <v>95</v>
+        <v>21</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>218</v>
+        <v>49</v>
       </c>
       <c r="B83" t="s">
-        <v>217</v>
+        <v>48</v>
       </c>
       <c r="C83" t="s">
-        <v>219</v>
+        <v>13</v>
       </c>
       <c r="D83">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E83" t="s">
-        <v>53</v>
+        <v>14</v>
       </c>
       <c r="F83" t="s">
         <v>16</v>
       </c>
       <c r="G83" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="H83" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="I83" t="s">
         <v>19</v>
       </c>
       <c r="J83" t="s">
-        <v>135</v>
+        <v>15</v>
       </c>
       <c r="K83" t="s">
         <v>20</v>
@@ -4366,25 +4375,25 @@
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>221</v>
+        <v>50</v>
       </c>
       <c r="B84" t="s">
-        <v>220</v>
+        <v>46</v>
       </c>
       <c r="C84" t="s">
-        <v>222</v>
+        <v>13</v>
       </c>
       <c r="D84">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E84" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F84" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="G84" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="H84" t="s">
         <v>15</v>
@@ -4404,72 +4413,72 @@
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>224</v>
+        <v>52</v>
       </c>
       <c r="B85" t="s">
-        <v>223</v>
+        <v>51</v>
       </c>
       <c r="C85" t="s">
-        <v>59</v>
+        <v>13</v>
       </c>
       <c r="D85">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E85" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="F85" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="G85" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="H85" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="I85" t="s">
         <v>19</v>
       </c>
       <c r="J85" t="s">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="K85" t="s">
         <v>20</v>
       </c>
       <c r="L85" t="s">
-        <v>90</v>
+        <v>21</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>226</v>
+        <v>62</v>
       </c>
       <c r="B86" t="s">
-        <v>225</v>
+        <v>61</v>
       </c>
       <c r="C86" t="s">
-        <v>227</v>
+        <v>59</v>
       </c>
       <c r="D86">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E86" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F86" t="s">
         <v>31</v>
       </c>
       <c r="G86" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="H86" t="s">
         <v>15</v>
       </c>
       <c r="I86" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J86" t="s">
-        <v>135</v>
+        <v>60</v>
       </c>
       <c r="K86" t="s">
         <v>20</v>
@@ -4480,25 +4489,25 @@
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>229</v>
+        <v>64</v>
       </c>
       <c r="B87" t="s">
-        <v>228</v>
+        <v>63</v>
       </c>
       <c r="C87" t="s">
-        <v>230</v>
+        <v>65</v>
       </c>
       <c r="D87">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E87" t="s">
-        <v>231</v>
+        <v>30</v>
       </c>
       <c r="F87" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="G87" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="H87" t="s">
         <v>15</v>
@@ -4507,36 +4516,36 @@
         <v>27</v>
       </c>
       <c r="J87" t="s">
-        <v>135</v>
+        <v>15</v>
       </c>
       <c r="K87" t="s">
-        <v>232</v>
+        <v>20</v>
       </c>
       <c r="L87" t="s">
-        <v>95</v>
+        <v>21</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>234</v>
+        <v>67</v>
       </c>
       <c r="B88" t="s">
-        <v>233</v>
+        <v>66</v>
       </c>
       <c r="C88" t="s">
-        <v>230</v>
+        <v>65</v>
       </c>
       <c r="D88">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E88" t="s">
-        <v>235</v>
+        <v>53</v>
       </c>
       <c r="F88" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="G88" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="H88" t="s">
         <v>15</v>
@@ -4545,74 +4554,71 @@
         <v>27</v>
       </c>
       <c r="J88" t="s">
-        <v>135</v>
+        <v>15</v>
       </c>
       <c r="K88" t="s">
-        <v>232</v>
+        <v>20</v>
       </c>
       <c r="L88" t="s">
-        <v>95</v>
+        <v>21</v>
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>237</v>
+        <v>69</v>
       </c>
       <c r="B89" t="s">
-        <v>236</v>
+        <v>68</v>
       </c>
       <c r="C89" t="s">
-        <v>230</v>
-      </c>
-      <c r="D89">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="E89" t="s">
-        <v>14</v>
+        <v>53</v>
       </c>
       <c r="F89" t="s">
         <v>16</v>
       </c>
       <c r="G89" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="H89" t="s">
         <v>15</v>
       </c>
       <c r="I89" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J89" t="s">
-        <v>135</v>
+        <v>15</v>
       </c>
       <c r="K89" t="s">
-        <v>232</v>
+        <v>20</v>
       </c>
       <c r="L89" t="s">
-        <v>95</v>
+        <v>21</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>239</v>
+        <v>71</v>
       </c>
       <c r="B90" t="s">
-        <v>238</v>
+        <v>70</v>
       </c>
       <c r="C90" t="s">
-        <v>230</v>
+        <v>72</v>
       </c>
       <c r="D90">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E90" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F90" t="s">
         <v>16</v>
       </c>
       <c r="G90" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="H90" t="s">
         <v>15</v>
@@ -4621,27 +4627,24 @@
         <v>27</v>
       </c>
       <c r="J90" t="s">
-        <v>135</v>
+        <v>15</v>
       </c>
       <c r="K90" t="s">
-        <v>232</v>
+        <v>20</v>
       </c>
       <c r="L90" t="s">
-        <v>95</v>
+        <v>21</v>
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>240</v>
+        <v>74</v>
       </c>
       <c r="B91" t="s">
-        <v>236</v>
+        <v>73</v>
       </c>
       <c r="C91" t="s">
-        <v>230</v>
-      </c>
-      <c r="D91">
-        <v>4</v>
+        <v>72</v>
       </c>
       <c r="E91" t="s">
         <v>14</v>
@@ -4650,7 +4653,7 @@
         <v>16</v>
       </c>
       <c r="G91" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="H91" t="s">
         <v>15</v>
@@ -4659,36 +4662,36 @@
         <v>27</v>
       </c>
       <c r="J91" t="s">
-        <v>135</v>
+        <v>15</v>
       </c>
       <c r="K91" t="s">
-        <v>232</v>
+        <v>20</v>
       </c>
       <c r="L91" t="s">
-        <v>95</v>
+        <v>21</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>242</v>
+        <v>76</v>
       </c>
       <c r="B92" t="s">
-        <v>241</v>
+        <v>75</v>
       </c>
       <c r="C92" t="s">
-        <v>230</v>
+        <v>72</v>
       </c>
       <c r="D92">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E92" t="s">
-        <v>212</v>
+        <v>77</v>
       </c>
       <c r="F92" t="s">
         <v>16</v>
       </c>
       <c r="G92" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="H92" t="s">
         <v>15</v>
@@ -4697,176 +4700,173 @@
         <v>27</v>
       </c>
       <c r="J92" t="s">
-        <v>135</v>
+        <v>15</v>
       </c>
       <c r="K92" t="s">
-        <v>232</v>
+        <v>20</v>
       </c>
       <c r="L92" t="s">
-        <v>95</v>
+        <v>21</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>244</v>
+        <v>79</v>
       </c>
       <c r="B93" t="s">
-        <v>243</v>
+        <v>78</v>
       </c>
       <c r="C93" t="s">
-        <v>230</v>
-      </c>
-      <c r="D93">
-        <v>4</v>
+        <v>72</v>
       </c>
       <c r="E93" t="s">
-        <v>231</v>
+        <v>34</v>
       </c>
       <c r="F93" t="s">
         <v>16</v>
       </c>
       <c r="G93" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="H93" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="I93" t="s">
         <v>27</v>
       </c>
       <c r="J93" t="s">
-        <v>135</v>
+        <v>15</v>
       </c>
       <c r="K93" t="s">
-        <v>232</v>
+        <v>20</v>
       </c>
       <c r="L93" t="s">
-        <v>90</v>
+        <v>21</v>
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>246</v>
+        <v>81</v>
       </c>
       <c r="B94" t="s">
-        <v>245</v>
+        <v>80</v>
       </c>
       <c r="C94" t="s">
-        <v>230</v>
+        <v>72</v>
       </c>
       <c r="D94">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E94" t="s">
-        <v>231</v>
+        <v>38</v>
       </c>
       <c r="F94" t="s">
         <v>16</v>
       </c>
       <c r="G94" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="H94" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="I94" t="s">
         <v>27</v>
       </c>
       <c r="J94" t="s">
-        <v>135</v>
+        <v>15</v>
       </c>
       <c r="K94" t="s">
-        <v>232</v>
+        <v>20</v>
       </c>
       <c r="L94" t="s">
-        <v>90</v>
+        <v>21</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>248</v>
+        <v>82</v>
       </c>
       <c r="B95" t="s">
-        <v>247</v>
+        <v>70</v>
       </c>
       <c r="C95" t="s">
-        <v>230</v>
+        <v>72</v>
       </c>
       <c r="D95">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E95" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="F95" t="s">
         <v>16</v>
       </c>
       <c r="G95" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="H95" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="I95" t="s">
         <v>27</v>
       </c>
       <c r="J95" t="s">
-        <v>135</v>
+        <v>15</v>
       </c>
       <c r="K95" t="s">
-        <v>232</v>
+        <v>20</v>
       </c>
       <c r="L95" t="s">
-        <v>90</v>
+        <v>21</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>250</v>
+        <v>84</v>
       </c>
       <c r="B96" t="s">
-        <v>249</v>
+        <v>83</v>
       </c>
       <c r="C96" t="s">
-        <v>230</v>
+        <v>72</v>
       </c>
       <c r="D96">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E96" t="s">
-        <v>30</v>
+        <v>85</v>
       </c>
       <c r="F96" t="s">
         <v>16</v>
       </c>
       <c r="G96" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="H96" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="I96" t="s">
         <v>27</v>
       </c>
       <c r="J96" t="s">
-        <v>135</v>
+        <v>15</v>
       </c>
       <c r="K96" t="s">
-        <v>232</v>
+        <v>20</v>
       </c>
       <c r="L96" t="s">
-        <v>90</v>
+        <v>21</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>251</v>
+        <v>12</v>
       </c>
       <c r="B97" t="s">
-        <v>247</v>
+        <v>11</v>
       </c>
       <c r="C97" t="s">
-        <v>230</v>
+        <v>13</v>
       </c>
       <c r="D97">
         <v>3</v>
@@ -4878,45 +4878,45 @@
         <v>16</v>
       </c>
       <c r="G97" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="H97" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="I97" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J97" t="s">
-        <v>135</v>
+        <v>15</v>
       </c>
       <c r="K97" t="s">
-        <v>232</v>
+        <v>20</v>
       </c>
       <c r="L97" t="s">
-        <v>90</v>
+        <v>21</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>253</v>
+        <v>88</v>
       </c>
       <c r="B98" t="s">
-        <v>252</v>
+        <v>87</v>
       </c>
       <c r="C98" t="s">
-        <v>230</v>
+        <v>72</v>
       </c>
       <c r="D98">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E98" t="s">
-        <v>212</v>
+        <v>34</v>
       </c>
       <c r="F98" t="s">
-        <v>16</v>
+        <v>89</v>
       </c>
       <c r="G98" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="H98" t="s">
         <v>26</v>
@@ -4925,10 +4925,10 @@
         <v>27</v>
       </c>
       <c r="J98" t="s">
-        <v>135</v>
+        <v>15</v>
       </c>
       <c r="K98" t="s">
-        <v>232</v>
+        <v>20</v>
       </c>
       <c r="L98" t="s">
         <v>90</v>
@@ -4936,25 +4936,25 @@
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>255</v>
+        <v>194</v>
       </c>
       <c r="B99" t="s">
-        <v>254</v>
+        <v>193</v>
       </c>
       <c r="C99" t="s">
-        <v>230</v>
+        <v>195</v>
       </c>
       <c r="D99">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E99" t="s">
-        <v>231</v>
+        <v>38</v>
       </c>
       <c r="F99" t="s">
-        <v>16</v>
+        <v>89</v>
       </c>
       <c r="G99" t="s">
-        <v>134</v>
+        <v>17</v>
       </c>
       <c r="H99" t="s">
         <v>18</v>
@@ -4966,7 +4966,7 @@
         <v>135</v>
       </c>
       <c r="K99" t="s">
-        <v>232</v>
+        <v>20</v>
       </c>
       <c r="L99" t="s">
         <v>95</v>
@@ -4974,25 +4974,25 @@
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>257</v>
+        <v>197</v>
       </c>
       <c r="B100" t="s">
-        <v>256</v>
+        <v>196</v>
       </c>
       <c r="C100" t="s">
-        <v>230</v>
+        <v>195</v>
       </c>
       <c r="D100">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E100" t="s">
-        <v>235</v>
+        <v>34</v>
       </c>
       <c r="F100" t="s">
-        <v>16</v>
+        <v>89</v>
       </c>
       <c r="G100" t="s">
-        <v>134</v>
+        <v>17</v>
       </c>
       <c r="H100" t="s">
         <v>18</v>
@@ -5004,7 +5004,7 @@
         <v>135</v>
       </c>
       <c r="K100" t="s">
-        <v>232</v>
+        <v>20</v>
       </c>
       <c r="L100" t="s">
         <v>95</v>
@@ -5012,43 +5012,47 @@
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>259</v>
+        <v>218</v>
       </c>
       <c r="B101" t="s">
-        <v>258</v>
+        <v>217</v>
       </c>
       <c r="C101" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="D101">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E101" t="s">
-        <v>14</v>
+        <v>53</v>
       </c>
       <c r="F101" t="s">
         <v>16</v>
       </c>
       <c r="G101" t="s">
-        <v>134</v>
+        <v>17</v>
       </c>
       <c r="H101" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="I101" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J101" t="s">
         <v>135</v>
       </c>
       <c r="K101" t="s">
-        <v>232</v>
+        <v>20</v>
       </c>
       <c r="L101" t="s">
-        <v>95</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:L102" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L101">
+    <sortCondition ref="G11:G101"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
